--- a/assets/liste-ventes-modele-en.xlsx
+++ b/assets/liste-ventes-modele-en.xlsx
@@ -76,7 +76,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
-    <numFmt numFmtId="165" formatCode="&quot;€&quot;#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
